--- a/report.xlsx
+++ b/report.xlsx
@@ -14,7 +14,7 @@
     <sheet name="元データ" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'検査結果'!$A$1:$B$6</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'検査結果'!$A$1:$B$8</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'列情報'!$A$1:$E$5</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'欠損行'!$A$1:$D$3</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'重複行'!$A$1:$D$3</definedName>
@@ -27,7 +27,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="3">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -39,8 +39,12 @@
       <b val="1"/>
       <color rgb="00FFFFFF"/>
     </font>
+    <font>
+      <b val="1"/>
+      <color rgb="009C0006"/>
+    </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill/>
     </fill>
@@ -50,6 +54,11 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="001F4E78"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFC7CE"/>
       </patternFill>
     </fill>
   </fills>
@@ -65,10 +74,16 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -435,11 +450,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B6"/>
+  <dimension ref="A1:B8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="13" customWidth="1" min="1" max="1"/>
+    <col width="21" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -457,57 +472,81 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>データ件数</t>
-        </is>
-      </c>
-      <c r="B2" t="n">
-        <v>5</v>
+          <t>検査したCSV</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>sample.csv</t>
+        </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>列数</t>
-        </is>
-      </c>
-      <c r="B3" t="n">
-        <v>4</v>
+          <t>検査日時</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-29 05:55:37</t>
+        </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>欠損セル数</t>
-        </is>
-      </c>
-      <c r="B4" t="n">
-        <v>2</v>
+          <t>データ件数</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>重複件数</t>
-        </is>
-      </c>
-      <c r="B5" t="n">
-        <v>1</v>
+          <t>列数</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
+          <t>欠損セル数</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>重複件数</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
           <t>総合判定</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
+      <c r="B8" s="3" t="inlineStr">
         <is>
           <t>問題あり</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:B6"/>
+  <autoFilter ref="A1:B8"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -523,7 +562,7 @@
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
     <col width="12" customWidth="1" min="2" max="2"/>
-    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
     <col width="12" customWidth="1" min="4" max="4"/>
     <col width="12" customWidth="1" min="5" max="5"/>
   </cols>
